--- a/survey_templates/028_mentorship_program_check_in_form--survey_templates.xlsx
+++ b/survey_templates/028_mentorship_program_check_in_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_1</t>
+          <t>program_status</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is the status of your mentorship program?</t>
+          <t>Current Status</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_2</t>
+          <t>challenges_faced</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What challenges have you faced in your mentorship program?</t>
+          <t>Challenges Faced</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_3</t>
+          <t>mentor_support</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What support have you received from your mentor?</t>
+          <t>Mentor Support</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_4</t>
+          <t>feedback_from_mentor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What feedback have you received from your mentor?</t>
+          <t>Feedback From Mentor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_5</t>
+          <t>next_steps</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>Next Steps</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_6</t>
+          <t>check_in_frequency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How often do you plan on checking in with your mentor?</t>
+          <t>Check-in Frequency</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_7</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Is there anything else you would like to add?</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_8</t>
+          <t>program_improvement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What are your next steps?</t>
+          <t>Program Improvement</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_9</t>
+          <t>other_comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>Other Comments</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_10</t>
+          <t>next_program_steps</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How can the program be improved?</t>
+          <t>Next Program Steps</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_11</t>
+          <t>program_status_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Do you have any other comments or questions?</t>
+          <t>Current Status (Again)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_12</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is the status of your mentorship program?</t>
+          <t>Challenges Faced 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_13</t>
+          <t>feedback_from_mentor_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What challenges have you faced in your mentorship program?</t>
+          <t>Feedback From Mentor 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_14</t>
+          <t>check_in_frequency_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What support have you received from your mentor?</t>
+          <t>Check In Frequency 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,246 +842,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_15</t>
+          <t>program_improvement_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What feedback have you received from your mentor?</t>
+          <t>Program Improvement 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional comments</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>How often do you plan on checking in with your mentor?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Is there anything else you would like to add?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What are your next steps?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Additional comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>How can the program be improved?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Do you have any other comments or questions?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What is the status of your mentorship program?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What challenges have you faced in your mentorship program?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What support have you received from your mentor?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +868,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +896,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_1_choices</t>
+          <t>program_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1136,14 +906,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>On schedule</t>
+          <t>On Schedule</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_1_choices</t>
+          <t>program_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1153,14 +923,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Behind schedule</t>
+          <t>Behind Schedule</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_1_choices</t>
+          <t>program_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1170,14 +940,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>At risk</t>
+          <t>At Risk</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_3_choices</t>
+          <t>mentor_support_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +964,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_3_choices</t>
+          <t>mentor_support_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +981,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_3_choices</t>
+          <t>mentor_support_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,228 +998,228 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_6_choices</t>
+          <t>next_steps_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>next_steps_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Next Steps 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_6_choices</t>
+          <t>next_steps_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>next_steps_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Next Steps 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_6_choices</t>
+          <t>next_steps_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>biweekly</t>
+          <t>next_steps_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Biweekly</t>
+          <t>Next Steps 3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_6_choices</t>
+          <t>check_in_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_8_choices</t>
+          <t>check_in_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>next_steps_1</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Next steps 1</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_8_choices</t>
+          <t>check_in_frequency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>next_steps_2</t>
+          <t>biweekly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Next steps 2</t>
+          <t>Biweekly</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_8_choices</t>
+          <t>check_in_frequency_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>next_steps_3</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Next steps 3</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_12_choices</t>
+          <t>next_program_steps_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>on_schedule</t>
+          <t>next_steps_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>On schedule</t>
+          <t>Next Steps 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_12_choices</t>
+          <t>next_program_steps_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>behind_schedule</t>
+          <t>next_steps_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Behind schedule</t>
+          <t>Next Steps 2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_12_choices</t>
+          <t>next_program_steps_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>at_risk</t>
+          <t>next_steps_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>At risk</t>
+          <t>Next Steps 3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_14_choices</t>
+          <t>program_status_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>on_schedule</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>On Schedule</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_14_choices</t>
+          <t>program_status_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>behind_schedule</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Behind Schedule</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_14_choices</t>
+          <t>program_status_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>bad</t>
+          <t>at_risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>At Risk</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_17_choices</t>
+          <t>check_in_frequency_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1236,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_17_choices</t>
+          <t>check_in_frequency_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1253,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_17_choices</t>
+          <t>check_in_frequency_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1270,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mentorship_program_check_in_form_section_17_choices</t>
+          <t>check_in_frequency_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1511,159 +1281,6 @@
       <c r="C24" t="inlineStr">
         <is>
           <t>Monthly</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_19_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>next_steps_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Next steps 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_19_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>next_steps_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Next steps 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_19_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>next_steps_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Next steps 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_23_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>on_schedule</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>On schedule</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_23_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>behind_schedule</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Behind schedule</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_23_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>at_risk</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_25_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_25_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>average</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>mentorship_program_check_in_form_section_25_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>bad</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Bad</t>
         </is>
       </c>
     </row>
